--- a/event_registration_forms/029_mother_s_day_raffle_form--event_registration_forms.xlsx
+++ b/event_registration_forms/029_mother_s_day_raffle_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1010,8 +1010,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'gift_card',_'value':_'gift_card'}</t>
+          <t>gift_card</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Gift Card', 'value': 'Gift Card'}</t>
+          <t>Gift Card</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'jewelry_set',_'value':_'jewelry_set'}</t>
+          <t>jewelry_set</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Jewelry Set', 'value': 'Jewelry Set'}</t>
+          <t>Jewelry Set</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'perfume',_'value':_'perfume'}</t>
+          <t>perfume</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Perfume', 'value': 'Perfume'}</t>
+          <t>Perfume</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'january',_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'January', 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'february',_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'February', 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'march',_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'March', 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'april',_'value':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'April', 'value': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'may',_'value':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'May', 'value': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'june',_'value':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'June', 'value': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'july',_'value':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'July', 'value': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'august',_'value':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'August', 'value': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'september',_'value':_9}</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'September', 'value': 9}</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'october',_'value':_10}</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'October', 'value': 10}</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'november',_'value':_11}</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'November', 'value': 11}</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'name':_'december',_'value':_12}</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'name': 'December', 'value': 12}</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name':_1,_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'name': 1, 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'name':_2,_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'name': 2, 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'name':_3,_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'name': 3, 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'name':_4,_'value':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'name': 4, 'value': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'name':_5,_'value':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'name': 5, 'value': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'name':_6,_'value':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'name': 6, 'value': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'name':_7,_'value':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'name': 7, 'value': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'name':_8,_'value':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'name': 8, 'value': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'name':_9,_'value':_9}</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'name': 9, 'value': 9}</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'name':_10,_'value':_10}</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'name': 10, 'value': 10}</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'name':_11,_'value':_11}</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'name': 11, 'value': 11}</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'name':_12,_'value':_12}</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'name': 12, 'value': 12}</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'name':_13,_'value':_13}</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'name': 13, 'value': 13}</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'name':_14,_'value':_14}</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'name': 14, 'value': 14}</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'name':_15,_'value':_15}</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'name': 15, 'value': 15}</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -1549,12 +1549,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'name':_16,_'value':_16}</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'name': 16, 'value': 16}</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'name':_17,_'value':_17}</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'name': 17, 'value': 17}</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -1583,12 +1583,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'name':_18,_'value':_18}</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'name': 18, 'value': 18}</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'name':_19,_'value':_19}</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'name': 19, 'value': 19}</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'name':_20,_'value':_20}</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'name': 20, 'value': 20}</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'name':_21,_'value':_21}</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'name': 21, 'value': 21}</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'name':_22,_'value':_22}</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'name': 22, 'value': 22}</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1668,12 +1668,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'name':_23,_'value':_23}</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'name': 23, 'value': 23}</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1685,12 +1685,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'name':_24,_'value':_24}</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'name': 24, 'value': 24}</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'name':_25,_'value':_25}</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'name': 25, 'value': 25}</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1719,12 +1719,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'name':_26,_'value':_26}</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'name': 26, 'value': 26}</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'name':_27,_'value':_27}</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'name': 27, 'value': 27}</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'name':_28,_'value':_28}</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'name': 28, 'value': 28}</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1770,12 +1770,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'name':_29,_'value':_29}</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'name': 29, 'value': 29}</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1787,12 +1787,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'name':_30,_'value':_30}</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'name': 30, 'value': 30}</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'name':_31,_'value':_31}</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'name': 31, 'value': 31}</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -1821,12 +1821,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'name':_1980,_'value':_1980}</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'name': 1980, 'value': 1980}</t>
+          <t>1980</t>
         </is>
       </c>
     </row>
@@ -1838,12 +1838,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'name':_1981,_'value':_1981}</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'name': 1981, 'value': 1981}</t>
+          <t>1981</t>
         </is>
       </c>
     </row>
@@ -1855,12 +1855,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'name':_1982,_'value':_1982}</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'name': 1982, 'value': 1982}</t>
+          <t>1982</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'name':_1983,_'value':_1983}</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'name': 1983, 'value': 1983}</t>
+          <t>1983</t>
         </is>
       </c>
     </row>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'name':_1984,_'value':_1984}</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'name': 1984, 'value': 1984}</t>
+          <t>1984</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1906,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'name':_1985,_'value':_1985}</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'name': 1985, 'value': 1985}</t>
+          <t>1985</t>
         </is>
       </c>
     </row>
@@ -1923,12 +1923,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'name':_1986,_'value':_1986}</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'name': 1986, 'value': 1986}</t>
+          <t>1986</t>
         </is>
       </c>
     </row>
@@ -1940,12 +1940,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'name':_1987,_'value':_1987}</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'name': 1987, 'value': 1987}</t>
+          <t>1987</t>
         </is>
       </c>
     </row>
@@ -1957,12 +1957,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'name':_1988,_'value':_1988}</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'name': 1988, 'value': 1988}</t>
+          <t>1988</t>
         </is>
       </c>
     </row>
@@ -1974,12 +1974,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'name':_1989,_'value':_1989}</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'name': 1989, 'value': 1989}</t>
+          <t>1989</t>
         </is>
       </c>
     </row>
@@ -1991,12 +1991,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'name':_1990,_'value':_1990}</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'name': 1990, 'value': 1990}</t>
+          <t>1990</t>
         </is>
       </c>
     </row>
@@ -2008,12 +2008,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'name':_1991,_'value':_1991}</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'name': 1991, 'value': 1991}</t>
+          <t>1991</t>
         </is>
       </c>
     </row>
@@ -2025,12 +2025,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'name':_1992,_'value':_1992}</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'name': 1992, 'value': 1992}</t>
+          <t>1992</t>
         </is>
       </c>
     </row>
@@ -2042,12 +2042,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'name':_1993,_'value':_1993}</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'name': 1993, 'value': 1993}</t>
+          <t>1993</t>
         </is>
       </c>
     </row>
@@ -2059,12 +2059,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'name':_1994,_'value':_1994}</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'name': 1994, 'value': 1994}</t>
+          <t>1994</t>
         </is>
       </c>
     </row>
@@ -2076,12 +2076,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'name':_1995,_'value':_1995}</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'name': 1995, 'value': 1995}</t>
+          <t>1995</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'name':_'active',_'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'name': 'Active', 'value': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'name':_'inactive',_'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'name': 'Inactive', 'value': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -2127,12 +2127,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'name':_'potential',_'value':_'potential'}</t>
+          <t>potential</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'name': 'Potential', 'value': 'Potential'}</t>
+          <t>Potential</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'name':_'lost',_'value':_'lost'}</t>
+          <t>lost</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'name': 'Lost', 'value': 'Lost'}</t>
+          <t>Lost</t>
         </is>
       </c>
     </row>
